--- a/data/trans_dic/IP1011-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1011-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen sindrome de down</t>
+          <t>Menores que padecen sindrome de down (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,08</t>
+          <t>0,12; 1,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,32</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,12</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,76</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,37 +1118,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,08; 0,73</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,62</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,18</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,81</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,62</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,53</t>
+          <t>0,0; 0,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,55</t>
+          <t>0,09; 0,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1157,7 +1158,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,25</t>
+          <t>0,0; 0,28</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen sindrome de down (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3025</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3807</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4680</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3795</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4064</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>601; 5738</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4435</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4264</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3069</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3304</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4019</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3309</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3571</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5300</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3920</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3236</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2735</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3922</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4963</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>602; 5250</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4641</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3563</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1273; 7062</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>674; 6809</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4099</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1011-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1011-Edad-trans_dic.xlsx
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,13</t>
+          <t>0,12; 1,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,32 +1133,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,73</t>
+          <t>0,08; 0,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,48</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,5</t>
+          <t>0,09; 0,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,47</t>
+          <t>0,05; 0,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,28</t>
+          <t>0,0; 0,27</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3025</t>
+          <t>0; 3036</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3807</t>
+          <t>0; 3510</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1595,32 +1595,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4680</t>
+          <t>0; 4523</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3795</t>
+          <t>0; 3791</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4064</t>
+          <t>0; 4107</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>601; 5738</t>
+          <t>601; 6154</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4435</t>
+          <t>0; 4809</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4264</t>
+          <t>0; 3603</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3069</t>
+          <t>0; 3274</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3304</t>
+          <t>0; 3737</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4019</t>
+          <t>0; 3350</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3309</t>
+          <t>0; 4332</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3571</t>
+          <t>0; 3428</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5300</t>
+          <t>0; 4727</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3920</t>
+          <t>0; 4475</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3922</t>
+          <t>0; 5134</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4963</t>
+          <t>0; 4813</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2084,32 +2084,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>602; 5250</t>
+          <t>602; 5312</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4641</t>
+          <t>0; 5042</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3563</t>
+          <t>0; 2878</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1273; 7062</t>
+          <t>1210; 7551</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>674; 6809</t>
+          <t>661; 6939</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4099</t>
+          <t>0; 3914</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1011-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1011-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,24%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,83</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,46</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,38</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,5</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,78</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,21</t>
+          <t>0,12; 1,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
     </row>
@@ -850,22 +850,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,27 +955,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,08; 0,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,74</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,54</t>
+          <t>0,09; 0,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,48</t>
+          <t>0,05; 0,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,25</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1474,22 +1474,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>605</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>756</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3036</t>
+          <t>0; 4647</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3510</t>
+          <t>0; 3898</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3564</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4523</t>
+          <t>0; 3039</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3791</t>
+          <t>0; 4090</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4107</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>601; 6154</t>
+          <t>601; 5452</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4809</t>
+          <t>0; 5760</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3603</t>
+          <t>0; 3359</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>651</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2653</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3274</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3737</t>
+          <t>0; 3244</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1805,22 +1805,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,27 +1853,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>656</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3350</t>
+          <t>0; 3733</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4332</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3428</t>
+          <t>0; 3759</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3707</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4727</t>
+          <t>0; 4464</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4475</t>
+          <t>0; 2661</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1963,24 +1963,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1266</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1412</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5134</t>
+          <t>601; 5849</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4813</t>
+          <t>0; 4606</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3938</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>602; 5312</t>
+          <t>0; 4386</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5042</t>
+          <t>0; 4369</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2878</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1210; 7551</t>
+          <t>1266; 7711</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>661; 6939</t>
+          <t>673; 6783</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3914</t>
+          <t>0; 3553</t>
         </is>
       </c>
     </row>
